--- a/jira/fm.xlsx
+++ b/jira/fm.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enable Secure Boot Support for Embedded Controller Firmware</t>
+          <t>Enable Secure Boot Support in Firmware</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,37 +518,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Add Secure Boot capability to the embedded controller firmware to ensure only signed firmware images are executed during device startup.</t>
+          <t>Add Secure Boot functionality to the firmware to ensure only signed and trusted code is executed during system startup.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Enhances device security by preventing unauthorized or malicious firmware from running, aligning with enterprise security standards.</t>
+          <t>Enhances platform security by preventing unauthorized code execution and protecting against malware at boot.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Reduces risk of firmware attacks, increases customer trust, and meets compliance requirements for secure devices.</t>
+          <t>Improved system integrity and compliance with enterprise security standards.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Device startup should be seamless and secure, with no noticeable delay or user intervention required.</t>
+          <t>System should boot securely and transparently for end users.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Embedded controller firmware; Secure Boot implementation; signature verification process.</t>
+          <t>Firmware boot process; integration with platform security modules.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Firmware must reject unsigned images and boot only signed firmware.</t>
+          <t>Secure Boot enabled and verified on all supported hardware.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Zero unsigned firmware execution; seamless Secure Boot integration.</t>
+          <t>100% Secure Boot coverage across Victoria platforms.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -558,24 +558,24 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Cryptographic library; Secure Boot keys provisioning; Firmware signing infrastructure.</t>
+          <t>Platform security modules; signed firmware images; hardware support for Secure Boot</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Security Engineering; Embedded Controller Firmware Team; Platform Validation</t>
+          <t>Security Engineering; Platform Hardware Team</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>HIGH WANT</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Add Battery Health Reporting to System Firmware</t>
+          <t>Optimize Firmware Update Process for Reduced Downtime</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,42 +585,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Diagnostics</t>
+          <t>Update &amp; Maintenance</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Implement battery health status reporting in system firmware, exposing metrics such as cycle count, capacity, and degradation to OS and management tools.</t>
+          <t>Improve the firmware update mechanism to minimize system downtime during updates.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Provides proactive diagnostics for battery maintenance, reducing unexpected failures and improving user satisfaction.</t>
+          <t>Reduces operational disruption and enhances user satisfaction during maintenance cycles.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enables predictive maintenance, reduces warranty costs, and improves device reliability.</t>
+          <t>Faster updates, less impact on productivity, and improved reliability.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Users and IT admins should be able to view battery health information easily through OS interfaces and management tools.</t>
+          <t>Users should experience minimal interruption during firmware updates.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>System firmware; battery health metrics collection; interface to OS and management tools.</t>
+          <t>Firmware update process; scheduling and rollback capabilities.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Battery health metrics available via standard OS APIs.</t>
+          <t>Downtime during update not to exceed 2 minutes.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Accurate battery health reporting with less than 5% error margin.</t>
+          <t>Seamless update experience with zero perceived downtime.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -630,17 +630,89 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Battery sensor integration; OS API support; Management tool compatibility.</t>
+          <t>Update scheduling logic; rollback mechanisms; platform integration</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>System Firmware Team; Battery Hardware Team; IT Management Solutions</t>
+          <t>Firmware Team; IT Operations</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Add Support for New Peripheral Device in Firmware</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Carlos Rivera</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Integrate support for the new XYZ peripheral device within the firmware.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Expands platform compatibility and enables new use cases for Victoria systems.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Broader device support, increased customer satisfaction, and market competitiveness.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Peripheral device should be recognized and function seamlessly upon connection.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Device detection, driver integration, and firmware communication protocols.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Peripheral device operates reliably in all tested scenarios.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Full compatibility with XYZ peripheral device.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>XYZ device specifications; driver development; QA testing</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Peripheral Vendor; QA Team; Firmware Development</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>HIGH WANT</t>
         </is>
       </c>
     </row>

--- a/jira/fm.xlsx
+++ b/jira/fm.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,17 +518,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Add Secure Boot functionality to the firmware to ensure only signed and trusted code is executed during system startup.</t>
+          <t>Add Secure Boot functionality to the firmware to ensure only trusted software is loaded during system startup.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Enhances platform security by preventing unauthorized code execution and protecting against malware at boot.</t>
+          <t>Enhances platform security by preventing unauthorized code execution at boot time.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Improved system integrity and compliance with enterprise security standards.</t>
+          <t>Reduces risk of malware and unauthorized firmware modifications, meeting enterprise security requirements.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -538,17 +538,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Firmware boot process; integration with platform security modules.</t>
+          <t>Implement Secure Boot validation in firmware startup sequence.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Secure Boot enabled and verified on all supported hardware.</t>
+          <t>Secure Boot enabled and validated on all supported platforms.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>100% Secure Boot coverage across Victoria platforms.</t>
+          <t>Full Secure Boot compliance with industry standards.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -558,12 +558,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Platform security modules; signed firmware images; hardware support for Secure Boot</t>
+          <t>Platform hardware support; Trusted Platform Module integration</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Security Engineering; Platform Hardware Team</t>
+          <t>Security Engineering; Platform Firmware Team</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Update &amp; Maintenance</t>
+          <t>Update</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Reduces operational disruption and enhances user satisfaction during maintenance cycles.</t>
+          <t>Reduces operational disruption and increases user satisfaction during firmware maintenance.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -610,17 +610,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Firmware update process; scheduling and rollback capabilities.</t>
+          <t>Optimize update scheduling, process efficiency, and rollback handling.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Downtime during update not to exceed 2 minutes.</t>
+          <t>Downtime during update is less than 2 minutes.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Seamless update experience with zero perceived downtime.</t>
+          <t>Downtime reduced to under 1 minute for typical updates.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -630,89 +630,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Update scheduling logic; rollback mechanisms; platform integration</t>
+          <t>Update infrastructure; Firmware rollback support</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Firmware Team; IT Operations</t>
+          <t>Firmware Update Team; QA</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Add Support for New Peripheral Device in Firmware</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Carlos Rivera</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Compatibility</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Integrate support for the new XYZ peripheral device within the firmware.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Expands platform compatibility and enables new use cases for Victoria systems.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Broader device support, increased customer satisfaction, and market competitiveness.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Peripheral device should be recognized and function seamlessly upon connection.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Device detection, driver integration, and firmware communication protocols.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Peripheral device operates reliably in all tested scenarios.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Full compatibility with XYZ peripheral device.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>XYZ device specifications; driver development; QA testing</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Peripheral Vendor; QA Team; Firmware Development</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>HIGH WANT</t>
         </is>
       </c>
     </row>
